--- a/outputs/D_phone_photo.xlsx
+++ b/outputs/D_phone_photo.xlsx
@@ -20,10 +20,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$L$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$313</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
@@ -2147,7 +2147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Perspective rectification inferred from a dominant table outline; verify row and column alignment.</t>
+          <t>Cell recheck at grid row 12, column 6: 'a' -&gt; '4'; compare source.</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Perspective rectification inferred from a dominant table outline; verify row and column alignment.</t>
+          <t>Cell recheck at grid row 12, column 6: 'a' -&gt; '4'; compare source.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>candidate_disagreement</t>
+          <t>layout_review</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Selected perspective-cell-recheck-300dpi; alternative deskew-300dpi produced different content or shape.</t>
+          <t>Perspective rectification inferred from a dominant table outline; verify row and column alignment.</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Compare the page and highlighted data.</t>
+          <t>Verify the source page and reconstructed cells.</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
@@ -2484,22 +2484,82 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
+          <t>layout_review</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Perspective rectification inferred from a dominant table outline; verify row and column alignment.</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Verify the source page and reconstructed cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
           <t>candidate_disagreement</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Selected perspective-cell-recheck-300dpi; alternative deskew-300dpi produced different content or shape.</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Compare the page and highlighted data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>candidate_disagreement</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Selected perspective-cell-recheck-300dpi; alternative cell-recheck-300dpi produced different content or shape.</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Compare the page and highlighted data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2607,7 +2667,7 @@
         <v>0.96</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>2.791</v>
+        <v>2.789</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2624,10 +2684,10 @@
         <v>8</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>-99.40000000000001</v>
+        <v>-78.40000000000001</v>
       </c>
       <c r="L2" s="7" t="inlineStr"/>
     </row>
@@ -2649,7 +2709,7 @@
         <v>0.96</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>3.839</v>
+        <v>4.55</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -2666,10 +2726,10 @@
         <v>8</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>-91.40000000000001</v>
+        <v>-63.4</v>
       </c>
       <c r="L3" s="7" t="inlineStr"/>
     </row>
@@ -2691,7 +2751,7 @@
         <v>0.96</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>4.249</v>
+        <v>4.442</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -2708,7 +2768,7 @@
         <v>144</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>842.2</v>
@@ -2733,7 +2793,7 @@
         <v>0.96</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3.176</v>
+        <v>2.61</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -2775,7 +2835,7 @@
         <v>0.96</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3.25</v>
+        <v>2.478</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -2817,7 +2877,7 @@
         <v>0.96</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3.216</v>
+        <v>4.886</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -3406,7 +3466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3444,95 +3504,131 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>21.626</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
+        <v>23.195</v>
+      </c>
+    </row>
+    <row r="4" ht="119" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Yellow cells</t>
+          <t>Text encoding</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Review required. See Validation Report for the reason and source row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+          <t>All XLSX string fields use a reversible encoding: a literal backslash is doubled; XML-forbidden code points use a backslash followed by u and four hexadecimal digits. An underscore starting an OOXML escape-like sequence uses the same Unicode encoding. Decode left to right, treating each doubled backslash as one literal backslash. The full audit JSON and saved workspace retain the original strings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="68" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Source row</t>
+          <t>Long text</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Data row within the extracted source table, excluding detected headers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
+          <t>Values exceeding Excel's 32767-character cell limit show an explicit preview. The Long Text sheet preserves the complete encoded value in numbered chunks. Join its chunks in order before decoding the text encoding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="68" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Small numbers</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Extraction heuristic / OCR score, not a calibrated probability of correctness.</t>
+          <t>Numbers below Excel's normal floating-point range remain exact text. Numbers needing more than 12 decimal places use General formatting; percentages needing more than 12 display decimals remain text, avoiding a false zero.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Yellow cells</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ISO and unambiguous day-first dates are typed. Ambiguous dates stay text.</t>
+          <t>Review required. See Validation Report for the reason and source row.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Source row</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Source strings are stored as text. No source formulas are executed.</t>
+          <t>Data row within the extracted source table, excluding detected headers.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Cell evidence</t>
+          <t>Confidence</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+          <t>Extraction heuristic / OCR score, not a calibrated probability of correctness.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>ISO and unambiguous day-first dates are typed. Ambiguous dates stay text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Source strings are stored as text. No source formulas are executed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Cell evidence</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>Repair proposals</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Arithmetic-derived suggestions only. Source documents may contain errors. Never applied automatically.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3644,16 +3740,16 @@
         <v>1</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>69.795</v>
+        <v>69.708</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>100.174</v>
+        <v>98.327</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>149.863</v>
+        <v>149.933</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>122.368</v>
+        <v>124.227</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -3691,16 +3787,16 @@
         <v>2</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>69.795</v>
+        <v>69.708</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>100.174</v>
+        <v>98.327</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>149.863</v>
+        <v>149.933</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>122.368</v>
+        <v>124.227</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -3738,16 +3834,16 @@
         <v>1</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>149.072</v>
+        <v>149.002</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>98.755</v>
+        <v>96.911</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>233.894</v>
+        <v>233.946</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>121.003</v>
+        <v>122.86</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -3785,16 +3881,16 @@
         <v>2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>149.072</v>
+        <v>149.002</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>98.755</v>
+        <v>96.911</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>233.894</v>
+        <v>233.946</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>121.003</v>
+        <v>122.86</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -3832,16 +3928,16 @@
         <v>1</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>233.304</v>
+        <v>233.251</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>97.33499999999999</v>
+        <v>95.494</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>317.932</v>
+        <v>317.967</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>119.553</v>
+        <v>121.406</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
@@ -3879,16 +3975,16 @@
         <v>2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>233.304</v>
+        <v>233.251</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>97.33499999999999</v>
+        <v>95.494</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>317.932</v>
+        <v>317.967</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>119.553</v>
+        <v>121.406</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -3926,16 +4022,16 @@
         <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>317.542</v>
+        <v>317.508</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>96.15600000000001</v>
+        <v>94.31699999999999</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>387.791</v>
+        <v>387.811</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>118.102</v>
+        <v>119.953</v>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
@@ -3973,16 +4069,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>317.542</v>
+        <v>317.508</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>96.15600000000001</v>
+        <v>94.31699999999999</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>387.791</v>
+        <v>387.811</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>118.102</v>
+        <v>119.953</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
@@ -4020,16 +4116,16 @@
         <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>387.568</v>
+        <v>387.548</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>93.339</v>
+        <v>91.506</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>554.756</v>
+        <v>554.771</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>116.896</v>
+        <v>118.744</v>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
@@ -4037,7 +4133,7 @@
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
@@ -4067,16 +4163,16 @@
         <v>2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>387.568</v>
+        <v>387.548</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>93.339</v>
+        <v>91.506</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>554.756</v>
+        <v>554.771</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>116.896</v>
+        <v>118.744</v>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
@@ -4114,16 +4210,16 @@
         <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>554.585</v>
+        <v>554.569</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>92.48</v>
+        <v>90.648</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>605.7329999999999</v>
+        <v>605.759</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>114.017</v>
+        <v>115.86</v>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
@@ -4131,7 +4227,7 @@
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
@@ -4161,16 +4257,16 @@
         <v>2</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>554.585</v>
+        <v>554.569</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>92.48</v>
+        <v>90.648</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>605.7329999999999</v>
+        <v>605.759</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>114.017</v>
+        <v>115.86</v>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
@@ -4178,7 +4274,7 @@
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
@@ -4208,16 +4304,16 @@
         <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>605.442</v>
+        <v>605.4160000000001</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>91.389</v>
+        <v>89.559</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>670.492</v>
+        <v>670.5309999999999</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>113.139</v>
+        <v>114.98</v>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
@@ -4255,16 +4351,16 @@
         <v>2</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>605.442</v>
+        <v>605.4160000000001</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>91.389</v>
+        <v>89.559</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>670.492</v>
+        <v>670.5309999999999</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>113.139</v>
+        <v>114.98</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -4302,16 +4398,16 @@
         <v>1</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>670.048</v>
+        <v>670.009</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>90.145</v>
+        <v>88.318</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>744.337</v>
+        <v>744.3920000000001</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>112.024</v>
+        <v>113.863</v>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
@@ -4349,16 +4445,16 @@
         <v>2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>670.048</v>
+        <v>670.009</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>90.145</v>
+        <v>88.318</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>744.337</v>
+        <v>744.3920000000001</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>112.024</v>
+        <v>113.863</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -4396,16 +4492,16 @@
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>743.72</v>
+        <v>743.665</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>89.063</v>
+        <v>87.238</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>808.576</v>
+        <v>808.645</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>110.752</v>
+        <v>112.589</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
@@ -4443,16 +4539,16 @@
         <v>2</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>743.72</v>
+        <v>743.665</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>89.063</v>
+        <v>87.238</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>808.576</v>
+        <v>808.645</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>110.752</v>
+        <v>112.589</v>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
@@ -4490,16 +4586,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>807.8099999999999</v>
+        <v>807.742</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>88.056</v>
+        <v>86.233</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>868.322</v>
+        <v>868.402</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>109.646</v>
+        <v>111.48</v>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
@@ -4537,16 +4633,16 @@
         <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>807.8099999999999</v>
+        <v>807.742</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>88.056</v>
+        <v>86.233</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>868.322</v>
+        <v>868.402</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>109.646</v>
+        <v>111.48</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -4584,16 +4680,16 @@
         <v>1</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>867.415</v>
+        <v>867.335</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>86.66500000000001</v>
+        <v>84.845</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>950.855</v>
+        <v>950.953</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>108.617</v>
+        <v>110.449</v>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
@@ -4631,16 +4727,16 @@
         <v>2</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>867.415</v>
+        <v>867.335</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>86.66500000000001</v>
+        <v>84.845</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>950.855</v>
+        <v>950.953</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>108.617</v>
+        <v>110.449</v>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
@@ -4678,16 +4774,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>949.7569999999999</v>
+        <v>949.659</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>85.13200000000001</v>
+        <v>83.315</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>1041.844</v>
+        <v>1041.961</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>107.196</v>
+        <v>109.025</v>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
@@ -4725,16 +4821,16 @@
         <v>2</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>949.7569999999999</v>
+        <v>949.659</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>85.13200000000001</v>
+        <v>83.315</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>1041.844</v>
+        <v>1041.961</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>107.196</v>
+        <v>109.025</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -4775,10 +4871,10 @@
         <v>68.547</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>121.003</v>
+        <v>122.86</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>149.072</v>
+        <v>149.002</v>
       </c>
       <c r="H26" s="7" t="n">
         <v>148.933</v>
@@ -4789,7 +4885,7 @@
         </is>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
@@ -4826,10 +4922,10 @@
         <v>148.065</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>119.553</v>
+        <v>121.406</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>233.304</v>
+        <v>233.251</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>147.53</v>
@@ -4877,10 +4973,10 @@
         <v>232.553</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>118.102</v>
+        <v>119.953</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>317.542</v>
+        <v>317.508</v>
       </c>
       <c r="H28" s="7" t="n">
         <v>146.039</v>
@@ -4928,10 +5024,10 @@
         <v>317.046</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>116.896</v>
+        <v>118.744</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>387.568</v>
+        <v>387.548</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>144.548</v>
@@ -4979,7 +5075,7 @@
         <v>387.283</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>114.017</v>
+        <v>115.86</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>554.974</v>
@@ -4993,7 +5089,7 @@
         </is>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
@@ -5027,10 +5123,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>554.756</v>
+        <v>554.771</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>113.139</v>
+        <v>114.98</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>606.104</v>
@@ -5078,10 +5174,10 @@
         <v>1</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>605.7329999999999</v>
+        <v>605.759</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>112.024</v>
+        <v>113.863</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>671.057</v>
@@ -5095,7 +5191,7 @@
         </is>
       </c>
       <c r="J32" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
@@ -5129,10 +5225,10 @@
         <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>670.492</v>
+        <v>670.5309999999999</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>110.752</v>
+        <v>112.589</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>745.122</v>
@@ -5146,7 +5242,7 @@
         </is>
       </c>
       <c r="J33" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
@@ -5180,10 +5276,10 @@
         <v>1</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>744.337</v>
+        <v>744.3920000000001</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>109.646</v>
+        <v>111.48</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>809.553</v>
@@ -5231,10 +5327,10 @@
         <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>808.576</v>
+        <v>808.645</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>108.617</v>
+        <v>110.449</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>869.476</v>
@@ -5282,10 +5378,10 @@
         <v>1</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>868.322</v>
+        <v>868.402</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>107.196</v>
+        <v>109.025</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>952.254</v>
@@ -5333,10 +5429,10 @@
         <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>950.855</v>
+        <v>950.953</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>105.629</v>
+        <v>107.455</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1043.512</v>
@@ -6013,7 +6109,7 @@
         </is>
       </c>
       <c r="J50" s="7" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
@@ -6268,7 +6364,7 @@
         </is>
       </c>
       <c r="J55" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
@@ -8410,7 +8506,7 @@
         </is>
       </c>
       <c r="J97" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
@@ -9073,7 +9169,7 @@
         </is>
       </c>
       <c r="J110" s="7" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
@@ -11164,7 +11260,7 @@
         </is>
       </c>
       <c r="J151" s="7" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="K151" s="7" t="inlineStr">
         <is>
@@ -11173,7 +11269,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>a</t>
         </is>
       </c>
       <c r="M151" s="7" t="inlineStr">
@@ -11521,7 +11617,7 @@
         </is>
       </c>
       <c r="J158" s="7" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="K158" s="7" t="inlineStr">
         <is>
@@ -12119,10 +12215,10 @@
         <v>68.547</v>
       </c>
       <c r="F170" s="7" t="n">
-        <v>121.003</v>
+        <v>122.86</v>
       </c>
       <c r="G170" s="7" t="n">
-        <v>149.072</v>
+        <v>149.002</v>
       </c>
       <c r="H170" s="7" t="n">
         <v>148.933</v>
@@ -12133,7 +12229,7 @@
         </is>
       </c>
       <c r="J170" s="7" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="K170" s="7" t="inlineStr">
         <is>
@@ -12170,10 +12266,10 @@
         <v>148.065</v>
       </c>
       <c r="F171" s="7" t="n">
-        <v>119.553</v>
+        <v>121.406</v>
       </c>
       <c r="G171" s="7" t="n">
-        <v>233.304</v>
+        <v>233.251</v>
       </c>
       <c r="H171" s="7" t="n">
         <v>147.53</v>
@@ -12221,10 +12317,10 @@
         <v>232.553</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>118.102</v>
+        <v>119.953</v>
       </c>
       <c r="G172" s="7" t="n">
-        <v>317.542</v>
+        <v>317.508</v>
       </c>
       <c r="H172" s="7" t="n">
         <v>146.039</v>
@@ -12235,7 +12331,7 @@
         </is>
       </c>
       <c r="J172" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K172" s="7" t="inlineStr">
         <is>
@@ -12272,10 +12368,10 @@
         <v>317.046</v>
       </c>
       <c r="F173" s="7" t="n">
-        <v>116.896</v>
+        <v>118.744</v>
       </c>
       <c r="G173" s="7" t="n">
-        <v>387.568</v>
+        <v>387.548</v>
       </c>
       <c r="H173" s="7" t="n">
         <v>144.548</v>
@@ -12323,7 +12419,7 @@
         <v>387.283</v>
       </c>
       <c r="F174" s="7" t="n">
-        <v>114.017</v>
+        <v>115.86</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>554.974</v>
@@ -12337,7 +12433,7 @@
         </is>
       </c>
       <c r="J174" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="K174" s="7" t="inlineStr">
         <is>
@@ -12371,10 +12467,10 @@
         <v>2</v>
       </c>
       <c r="E175" s="7" t="n">
-        <v>554.756</v>
+        <v>554.771</v>
       </c>
       <c r="F175" s="7" t="n">
-        <v>113.139</v>
+        <v>114.98</v>
       </c>
       <c r="G175" s="7" t="n">
         <v>606.104</v>
@@ -12422,10 +12518,10 @@
         <v>2</v>
       </c>
       <c r="E176" s="7" t="n">
-        <v>605.7329999999999</v>
+        <v>605.759</v>
       </c>
       <c r="F176" s="7" t="n">
-        <v>112.024</v>
+        <v>113.863</v>
       </c>
       <c r="G176" s="7" t="n">
         <v>671.057</v>
@@ -12473,10 +12569,10 @@
         <v>2</v>
       </c>
       <c r="E177" s="7" t="n">
-        <v>670.492</v>
+        <v>670.5309999999999</v>
       </c>
       <c r="F177" s="7" t="n">
-        <v>110.752</v>
+        <v>112.589</v>
       </c>
       <c r="G177" s="7" t="n">
         <v>745.122</v>
@@ -12524,10 +12620,10 @@
         <v>2</v>
       </c>
       <c r="E178" s="7" t="n">
-        <v>744.337</v>
+        <v>744.3920000000001</v>
       </c>
       <c r="F178" s="7" t="n">
-        <v>109.646</v>
+        <v>111.48</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>809.553</v>
@@ -12575,10 +12671,10 @@
         <v>2</v>
       </c>
       <c r="E179" s="7" t="n">
-        <v>808.576</v>
+        <v>808.645</v>
       </c>
       <c r="F179" s="7" t="n">
-        <v>108.617</v>
+        <v>110.449</v>
       </c>
       <c r="G179" s="7" t="n">
         <v>869.476</v>
@@ -12626,10 +12722,10 @@
         <v>2</v>
       </c>
       <c r="E180" s="7" t="n">
-        <v>868.322</v>
+        <v>868.402</v>
       </c>
       <c r="F180" s="7" t="n">
-        <v>107.196</v>
+        <v>109.025</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>952.254</v>
@@ -12677,10 +12773,10 @@
         <v>2</v>
       </c>
       <c r="E181" s="7" t="n">
-        <v>950.855</v>
+        <v>950.953</v>
       </c>
       <c r="F181" s="7" t="n">
-        <v>105.629</v>
+        <v>107.455</v>
       </c>
       <c r="G181" s="7" t="n">
         <v>1043.512</v>
@@ -12745,7 +12841,7 @@
         </is>
       </c>
       <c r="J182" s="7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="K182" s="7" t="inlineStr">
         <is>
@@ -12847,7 +12943,7 @@
         </is>
       </c>
       <c r="J184" s="7" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="K184" s="7" t="inlineStr">
         <is>
@@ -12949,7 +13045,7 @@
         </is>
       </c>
       <c r="J186" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K186" s="7" t="inlineStr">
         <is>
@@ -13051,7 +13147,7 @@
         </is>
       </c>
       <c r="J188" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K188" s="7" t="inlineStr">
         <is>
@@ -13357,7 +13453,7 @@
         </is>
       </c>
       <c r="J194" s="7" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="K194" s="7" t="inlineStr">
         <is>
@@ -13408,7 +13504,7 @@
         </is>
       </c>
       <c r="J195" s="7" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="K195" s="7" t="inlineStr">
         <is>
@@ -13459,7 +13555,7 @@
         </is>
       </c>
       <c r="J196" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K196" s="7" t="inlineStr">
         <is>
@@ -13510,7 +13606,7 @@
         </is>
       </c>
       <c r="J197" s="7" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="K197" s="7" t="inlineStr">
         <is>
@@ -13663,7 +13759,7 @@
         </is>
       </c>
       <c r="J200" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K200" s="7" t="inlineStr">
         <is>
@@ -13714,7 +13810,7 @@
         </is>
       </c>
       <c r="J201" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K201" s="7" t="inlineStr">
         <is>
@@ -13969,7 +14065,7 @@
         </is>
       </c>
       <c r="J206" s="7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="K206" s="7" t="inlineStr">
         <is>
@@ -14173,7 +14269,7 @@
         </is>
       </c>
       <c r="J210" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K210" s="7" t="inlineStr">
         <is>
@@ -14428,7 +14524,7 @@
         </is>
       </c>
       <c r="J215" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K215" s="7" t="inlineStr">
         <is>
@@ -14581,7 +14677,7 @@
         </is>
       </c>
       <c r="J218" s="7" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="K218" s="7" t="inlineStr">
         <is>
@@ -14683,7 +14779,7 @@
         </is>
       </c>
       <c r="J220" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K220" s="7" t="inlineStr">
         <is>
@@ -14734,7 +14830,7 @@
         </is>
       </c>
       <c r="J221" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K221" s="7" t="inlineStr">
         <is>
@@ -15142,7 +15238,7 @@
         </is>
       </c>
       <c r="J229" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K229" s="7" t="inlineStr">
         <is>
@@ -15397,7 +15493,7 @@
         </is>
       </c>
       <c r="J234" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K234" s="7" t="inlineStr">
         <is>
@@ -15805,7 +15901,7 @@
         </is>
       </c>
       <c r="J242" s="7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="K242" s="7" t="inlineStr">
         <is>
@@ -15907,7 +16003,7 @@
         </is>
       </c>
       <c r="J244" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K244" s="7" t="inlineStr">
         <is>
@@ -16009,7 +16105,7 @@
         </is>
       </c>
       <c r="J246" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K246" s="7" t="inlineStr">
         <is>
@@ -16162,7 +16258,7 @@
         </is>
       </c>
       <c r="J249" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K249" s="7" t="inlineStr">
         <is>
@@ -16417,7 +16513,7 @@
         </is>
       </c>
       <c r="J254" s="7" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="K254" s="7" t="inlineStr">
         <is>
@@ -16519,7 +16615,7 @@
         </is>
       </c>
       <c r="J256" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K256" s="7" t="inlineStr">
         <is>
@@ -16621,7 +16717,7 @@
         </is>
       </c>
       <c r="J258" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K258" s="7" t="inlineStr">
         <is>
@@ -17794,7 +17890,7 @@
         </is>
       </c>
       <c r="J281" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K281" s="7" t="inlineStr">
         <is>
@@ -18253,7 +18349,7 @@
         </is>
       </c>
       <c r="J290" s="7" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="K290" s="7" t="inlineStr">
         <is>
@@ -18355,7 +18451,7 @@
         </is>
       </c>
       <c r="J292" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K292" s="7" t="inlineStr">
         <is>
@@ -18457,7 +18553,7 @@
         </is>
       </c>
       <c r="J294" s="7" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="K294" s="7" t="inlineStr">
         <is>
@@ -18865,7 +18961,7 @@
         </is>
       </c>
       <c r="J302" s="7" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="K302" s="7" t="inlineStr">
         <is>
@@ -18967,7 +19063,7 @@
         </is>
       </c>
       <c r="J304" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K304" s="7" t="inlineStr">
         <is>
@@ -19120,7 +19216,7 @@
         </is>
       </c>
       <c r="J307" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K307" s="7" t="inlineStr">
         <is>
@@ -19495,7 +19591,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>79dc9b77d9e015b2073a662d9d263c23aa176856138730d8a000ea59085e4cb5</t>
+          <t>bc13068834538b1641a6d20212938df8e2d56b01e8dcd6366f0c522a872ecd6e</t>
         </is>
       </c>
     </row>

--- a/outputs/D_phone_photo.xlsx
+++ b/outputs/D_phone_photo.xlsx
@@ -10,25 +10,27 @@
     <sheet name="Data 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Validation Report" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Page Audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Join Receipt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cell Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Constraints" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Repair Proposals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Correction History" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$L$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$313</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$M$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2082,6 +2084,79 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting equations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -2667,7 +2742,7 @@
         <v>0.96</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>2.789</v>
+        <v>6.56</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2709,7 +2784,7 @@
         <v>0.96</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>4.55</v>
+        <v>8.907</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -2751,7 +2826,7 @@
         <v>0.96</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>4.442</v>
+        <v>9.641</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -2793,7 +2868,7 @@
         <v>0.96</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2.61</v>
+        <v>6.396</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -2835,7 +2910,7 @@
         <v>0.96</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>2.478</v>
+        <v>6.642</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -2877,7 +2952,7 @@
         <v>0.96</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4.886</v>
+        <v>9.022</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -2908,6 +2983,133 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Page joins</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Repeated headers removed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Split rows recovered</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PDF page</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source rows on page</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Output rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3460,7 +3662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3504,7 +3706,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>23.195</v>
+        <v>52.365</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -3633,7 +3835,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19546,7 +19748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19591,7 +19793,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>bc13068834538b1641a6d20212938df8e2d56b01e8dcd6366f0c522a872ecd6e</t>
+          <t>ad1b0e0037e348d336137ef88ca756f886fb2a05f5ee3b30ee1c6c4b6de3a67e</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19790,77 +19992,4 @@
   <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Excel row</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Supporting equations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/D_phone_photo.xlsx
+++ b/outputs/D_phone_photo.xlsx
@@ -26,8 +26,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$M$313</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$O$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
@@ -2742,7 +2742,7 @@
         <v>0.96</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>6.56</v>
+        <v>2.837</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>0.96</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>8.907</v>
+        <v>8.358000000000001</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>0.96</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>9.641</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>0.96</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>6.396</v>
+        <v>2.728</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>0.96</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>6.642</v>
+        <v>2.771</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>0.96</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>9.022</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>52.365</v>
+        <v>38.947</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -3841,7 +3841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M313"/>
+  <dimension ref="A1:O313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3857,6 +3857,8 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3925,6 +3927,16 @@
           <t>Role</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Location status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Location reason</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -3972,6 +3984,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -4019,6 +4041,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -4066,6 +4098,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -4113,6 +4155,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -4160,6 +4212,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -4207,6 +4269,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -4254,6 +4326,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -4301,6 +4383,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -4348,6 +4440,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -4395,6 +4497,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -4442,6 +4554,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -4489,6 +4611,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -4536,6 +4668,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -4583,6 +4725,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
@@ -4630,6 +4782,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -4677,6 +4839,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
@@ -4724,6 +4896,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -4771,6 +4953,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
@@ -4818,6 +5010,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -4865,6 +5067,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
@@ -4912,6 +5124,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -4959,6 +5181,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
@@ -5006,6 +5238,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -5053,6 +5295,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
@@ -5104,6 +5356,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -5155,6 +5417,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
@@ -5206,6 +5478,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -5257,6 +5539,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
@@ -5308,6 +5600,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
@@ -5359,6 +5661,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
@@ -5410,6 +5722,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
@@ -5461,6 +5783,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
@@ -5512,6 +5844,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
@@ -5563,6 +5905,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
@@ -5614,6 +5966,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -5665,6 +6027,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
@@ -5716,6 +6088,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
@@ -5767,6 +6149,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
@@ -5818,6 +6210,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
@@ -5869,6 +6271,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
@@ -5920,6 +6332,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
@@ -5971,6 +6393,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
@@ -6022,6 +6454,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
@@ -6073,6 +6515,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
@@ -6124,6 +6576,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
@@ -6175,6 +6637,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
@@ -6226,6 +6698,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
@@ -6277,6 +6759,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
@@ -6328,6 +6820,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O50" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
@@ -6379,6 +6881,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
@@ -6430,6 +6942,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O52" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
@@ -6481,6 +7003,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
@@ -6532,6 +7064,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="17" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
@@ -6583,6 +7125,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
@@ -6634,6 +7186,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
@@ -6685,6 +7247,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
@@ -6736,6 +7308,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="17" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
@@ -6787,6 +7369,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O59" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="17" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
@@ -6838,6 +7430,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="17" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
@@ -6889,6 +7491,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
@@ -6940,6 +7552,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="17" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
@@ -6991,6 +7613,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
@@ -7042,6 +7674,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="17" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
@@ -7093,6 +7735,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
@@ -7144,6 +7796,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="17" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
@@ -7195,6 +7857,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
@@ -7246,6 +7918,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="17" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
@@ -7297,6 +7979,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
@@ -7348,6 +8040,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O70" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="17" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
@@ -7399,6 +8101,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="17" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
@@ -7450,6 +8162,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O72" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="17" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
@@ -7501,6 +8223,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N73" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O73" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
@@ -7552,6 +8284,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O74" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
@@ -7603,6 +8345,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
@@ -7654,6 +8406,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O76" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="17" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
@@ -7705,6 +8467,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="17" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
@@ -7756,6 +8528,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N78" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O78" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="17" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
@@ -7807,6 +8589,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O79" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="17" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
@@ -7858,6 +8650,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N80" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O80" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="17" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
@@ -7909,6 +8711,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O81" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
@@ -7960,6 +8772,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N82" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O82" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="17" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
@@ -8011,6 +8833,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N83" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O83" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
@@ -8062,6 +8894,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N84" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O84" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="17" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
@@ -8113,6 +8955,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N85" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O85" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="17" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
@@ -8164,6 +9016,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O86" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="17" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
@@ -8215,6 +9077,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N87" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O87" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
@@ -8266,6 +9138,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N88" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O88" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="17" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
@@ -8317,6 +9199,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O89" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
@@ -8368,6 +9260,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O90" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="17" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
@@ -8419,6 +9321,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N91" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O91" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="17" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
@@ -8470,6 +9382,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N92" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O92" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="17" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
@@ -8521,6 +9443,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N93" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O93" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="17" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
@@ -8572,6 +9504,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N94" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O94" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="17" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
@@ -8623,6 +9565,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O95" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="17" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
@@ -8674,6 +9626,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N96" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O96" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="17" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
@@ -8725,6 +9687,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O97" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="17" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
@@ -8776,6 +9748,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N98" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O98" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="17" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
@@ -8827,6 +9809,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O99" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="17" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
@@ -8878,6 +9870,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N100" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O100" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="17" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
@@ -8929,6 +9931,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N101" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O101" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="17" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
@@ -8980,6 +9992,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N102" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O102" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="17" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
@@ -9031,6 +10053,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N103" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O103" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="17" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
@@ -9082,6 +10114,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N104" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O104" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="17" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
@@ -9133,6 +10175,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N105" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O105" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="17" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
@@ -9184,6 +10236,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N106" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O106" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="17" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
@@ -9235,6 +10297,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N107" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O107" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="17" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
@@ -9286,6 +10358,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N108" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O108" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="17" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
@@ -9337,6 +10419,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N109" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O109" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="17" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
@@ -9388,6 +10480,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N110" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O110" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="17" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
@@ -9439,6 +10541,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N111" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O111" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="17" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
@@ -9490,6 +10602,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N112" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O112" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="17" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
@@ -9541,6 +10663,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N113" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O113" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="17" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
@@ -9592,6 +10724,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N114" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O114" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="17" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
@@ -9643,6 +10785,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N115" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O115" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="17" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
@@ -9694,6 +10846,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N116" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O116" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="17" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
@@ -9745,6 +10907,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N117" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O117" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="17" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
@@ -9796,6 +10968,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N118" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O118" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="17" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
@@ -9847,6 +11029,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N119" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O119" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="17" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
@@ -9898,6 +11090,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N120" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O120" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="17" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
@@ -9949,6 +11151,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N121" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O121" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="17" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
@@ -10000,6 +11212,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N122" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O122" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="17" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
@@ -10051,6 +11273,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N123" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O123" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="17" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
@@ -10102,6 +11334,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N124" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O124" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="17" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
@@ -10153,6 +11395,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N125" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O125" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="17" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
@@ -10204,6 +11456,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N126" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O126" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="17" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
@@ -10255,6 +11517,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N127" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O127" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="17" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
@@ -10306,6 +11578,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N128" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O128" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="17" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
@@ -10357,6 +11639,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N129" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O129" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="17" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
@@ -10408,6 +11700,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N130" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O130" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="17" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
@@ -10459,6 +11761,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N131" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O131" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="17" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
@@ -10510,6 +11822,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N132" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O132" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="17" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
@@ -10561,6 +11883,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N133" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O133" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="17" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
@@ -10612,6 +11944,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N134" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O134" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="17" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
@@ -10663,6 +12005,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N135" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O135" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="17" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
@@ -10714,6 +12066,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N136" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O136" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="17" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
@@ -10765,6 +12127,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N137" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O137" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="17" customHeight="1">
       <c r="A138" s="7" t="inlineStr">
@@ -10816,6 +12188,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N138" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O138" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="17" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
@@ -10867,6 +12249,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N139" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O139" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="17" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
@@ -10918,6 +12310,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N140" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O140" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="17" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
@@ -10969,6 +12371,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N141" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O141" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="17" customHeight="1">
       <c r="A142" s="7" t="inlineStr">
@@ -11020,6 +12432,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N142" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O142" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="17" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
@@ -11071,6 +12493,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N143" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O143" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="17" customHeight="1">
       <c r="A144" s="7" t="inlineStr">
@@ -11122,6 +12554,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N144" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O144" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="17" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
@@ -11173,6 +12615,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N145" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O145" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="17" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
@@ -11224,6 +12676,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N146" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O146" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="17" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
@@ -11275,6 +12737,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N147" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O147" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="17" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
@@ -11326,6 +12798,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N148" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O148" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="17" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
@@ -11377,6 +12859,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N149" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O149" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="17" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
@@ -11428,6 +12920,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N150" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O150" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="17" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
@@ -11479,6 +12981,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N151" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O151" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="17" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
@@ -11530,6 +13042,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N152" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O152" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="17" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
@@ -11581,6 +13103,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N153" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O153" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="17" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
@@ -11632,6 +13164,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N154" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O154" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="17" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
@@ -11683,6 +13225,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N155" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O155" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="17" customHeight="1">
       <c r="A156" s="7" t="inlineStr">
@@ -11734,6 +13286,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N156" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O156" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="17" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
@@ -11785,6 +13347,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N157" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O157" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="17" customHeight="1">
       <c r="A158" s="7" t="inlineStr">
@@ -11836,6 +13408,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N158" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O158" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="17" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
@@ -11887,6 +13469,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N159" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O159" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="17" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
@@ -11938,6 +13530,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N160" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O160" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="17" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
@@ -11989,6 +13591,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N161" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O161" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="17" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
@@ -12040,6 +13652,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N162" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O162" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="17" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
@@ -12091,6 +13713,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N163" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O163" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="17" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
@@ -12142,6 +13774,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N164" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O164" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="17" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
@@ -12193,6 +13835,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N165" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O165" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="17" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
@@ -12244,6 +13896,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N166" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O166" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="17" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
@@ -12295,6 +13957,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N167" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O167" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="17" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
@@ -12346,6 +14018,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N168" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O168" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="17" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
@@ -12397,6 +14079,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N169" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O169" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="17" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
@@ -12448,6 +14140,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N170" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O170" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="17" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
@@ -12499,6 +14201,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N171" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O171" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="17" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
@@ -12550,6 +14262,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N172" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O172" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="17" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
@@ -12601,6 +14323,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N173" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O173" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="17" customHeight="1">
       <c r="A174" s="7" t="inlineStr">
@@ -12652,6 +14384,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N174" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O174" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="17" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
@@ -12703,6 +14445,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N175" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O175" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="17" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
@@ -12754,6 +14506,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N176" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O176" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="17" customHeight="1">
       <c r="A177" s="7" t="inlineStr">
@@ -12805,6 +14567,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N177" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O177" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="17" customHeight="1">
       <c r="A178" s="7" t="inlineStr">
@@ -12856,6 +14628,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N178" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O178" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="17" customHeight="1">
       <c r="A179" s="7" t="inlineStr">
@@ -12907,6 +14689,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N179" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O179" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="17" customHeight="1">
       <c r="A180" s="7" t="inlineStr">
@@ -12958,6 +14750,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N180" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O180" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="17" customHeight="1">
       <c r="A181" s="7" t="inlineStr">
@@ -13009,6 +14811,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N181" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O181" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="17" customHeight="1">
       <c r="A182" s="7" t="inlineStr">
@@ -13060,6 +14872,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N182" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O182" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="17" customHeight="1">
       <c r="A183" s="7" t="inlineStr">
@@ -13111,6 +14933,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N183" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O183" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="17" customHeight="1">
       <c r="A184" s="7" t="inlineStr">
@@ -13162,6 +14994,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N184" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O184" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="17" customHeight="1">
       <c r="A185" s="7" t="inlineStr">
@@ -13213,6 +15055,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N185" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O185" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="17" customHeight="1">
       <c r="A186" s="7" t="inlineStr">
@@ -13264,6 +15116,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N186" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O186" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="17" customHeight="1">
       <c r="A187" s="7" t="inlineStr">
@@ -13315,6 +15177,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N187" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O187" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="17" customHeight="1">
       <c r="A188" s="7" t="inlineStr">
@@ -13366,6 +15238,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N188" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O188" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="17" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
@@ -13417,6 +15299,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N189" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O189" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="17" customHeight="1">
       <c r="A190" s="7" t="inlineStr">
@@ -13468,6 +15360,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N190" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O190" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="17" customHeight="1">
       <c r="A191" s="7" t="inlineStr">
@@ -13519,6 +15421,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N191" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O191" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="17" customHeight="1">
       <c r="A192" s="7" t="inlineStr">
@@ -13570,6 +15482,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N192" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O192" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="17" customHeight="1">
       <c r="A193" s="7" t="inlineStr">
@@ -13621,6 +15543,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N193" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O193" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="17" customHeight="1">
       <c r="A194" s="7" t="inlineStr">
@@ -13672,6 +15604,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N194" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O194" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="17" customHeight="1">
       <c r="A195" s="7" t="inlineStr">
@@ -13723,6 +15665,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N195" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O195" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="17" customHeight="1">
       <c r="A196" s="7" t="inlineStr">
@@ -13774,6 +15726,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N196" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O196" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="17" customHeight="1">
       <c r="A197" s="7" t="inlineStr">
@@ -13825,6 +15787,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N197" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O197" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="17" customHeight="1">
       <c r="A198" s="7" t="inlineStr">
@@ -13876,6 +15848,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N198" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O198" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="17" customHeight="1">
       <c r="A199" s="7" t="inlineStr">
@@ -13927,6 +15909,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N199" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O199" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="17" customHeight="1">
       <c r="A200" s="7" t="inlineStr">
@@ -13978,6 +15970,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N200" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O200" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="17" customHeight="1">
       <c r="A201" s="7" t="inlineStr">
@@ -14029,6 +16031,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N201" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O201" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="17" customHeight="1">
       <c r="A202" s="7" t="inlineStr">
@@ -14080,6 +16092,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N202" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O202" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="17" customHeight="1">
       <c r="A203" s="7" t="inlineStr">
@@ -14131,6 +16153,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N203" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O203" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="17" customHeight="1">
       <c r="A204" s="7" t="inlineStr">
@@ -14182,6 +16214,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N204" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O204" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="17" customHeight="1">
       <c r="A205" s="7" t="inlineStr">
@@ -14233,6 +16275,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N205" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O205" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="17" customHeight="1">
       <c r="A206" s="7" t="inlineStr">
@@ -14284,6 +16336,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N206" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O206" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="17" customHeight="1">
       <c r="A207" s="7" t="inlineStr">
@@ -14335,6 +16397,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N207" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O207" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="17" customHeight="1">
       <c r="A208" s="7" t="inlineStr">
@@ -14386,6 +16458,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N208" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O208" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="17" customHeight="1">
       <c r="A209" s="7" t="inlineStr">
@@ -14437,6 +16519,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N209" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O209" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="17" customHeight="1">
       <c r="A210" s="7" t="inlineStr">
@@ -14488,6 +16580,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N210" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O210" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="17" customHeight="1">
       <c r="A211" s="7" t="inlineStr">
@@ -14539,6 +16641,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N211" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O211" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="17" customHeight="1">
       <c r="A212" s="7" t="inlineStr">
@@ -14590,6 +16702,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N212" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O212" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="17" customHeight="1">
       <c r="A213" s="7" t="inlineStr">
@@ -14641,6 +16763,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N213" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O213" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="17" customHeight="1">
       <c r="A214" s="7" t="inlineStr">
@@ -14692,6 +16824,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N214" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O214" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="17" customHeight="1">
       <c r="A215" s="7" t="inlineStr">
@@ -14743,6 +16885,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N215" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O215" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="17" customHeight="1">
       <c r="A216" s="7" t="inlineStr">
@@ -14794,6 +16946,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N216" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O216" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="17" customHeight="1">
       <c r="A217" s="7" t="inlineStr">
@@ -14845,6 +17007,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N217" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O217" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="17" customHeight="1">
       <c r="A218" s="7" t="inlineStr">
@@ -14896,6 +17068,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N218" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O218" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="17" customHeight="1">
       <c r="A219" s="7" t="inlineStr">
@@ -14947,6 +17129,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N219" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O219" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="17" customHeight="1">
       <c r="A220" s="7" t="inlineStr">
@@ -14998,6 +17190,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N220" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O220" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="17" customHeight="1">
       <c r="A221" s="7" t="inlineStr">
@@ -15049,6 +17251,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N221" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O221" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="17" customHeight="1">
       <c r="A222" s="7" t="inlineStr">
@@ -15100,6 +17312,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N222" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O222" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="17" customHeight="1">
       <c r="A223" s="7" t="inlineStr">
@@ -15151,6 +17373,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N223" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O223" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="17" customHeight="1">
       <c r="A224" s="7" t="inlineStr">
@@ -15202,6 +17434,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N224" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O224" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="17" customHeight="1">
       <c r="A225" s="7" t="inlineStr">
@@ -15253,6 +17495,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N225" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O225" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="17" customHeight="1">
       <c r="A226" s="7" t="inlineStr">
@@ -15304,6 +17556,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N226" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O226" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="17" customHeight="1">
       <c r="A227" s="7" t="inlineStr">
@@ -15355,6 +17617,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N227" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O227" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="17" customHeight="1">
       <c r="A228" s="7" t="inlineStr">
@@ -15406,6 +17678,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N228" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O228" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="17" customHeight="1">
       <c r="A229" s="7" t="inlineStr">
@@ -15457,6 +17739,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N229" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O229" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="17" customHeight="1">
       <c r="A230" s="7" t="inlineStr">
@@ -15508,6 +17800,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N230" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O230" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="17" customHeight="1">
       <c r="A231" s="7" t="inlineStr">
@@ -15559,6 +17861,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N231" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O231" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="17" customHeight="1">
       <c r="A232" s="7" t="inlineStr">
@@ -15610,6 +17922,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N232" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O232" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="17" customHeight="1">
       <c r="A233" s="7" t="inlineStr">
@@ -15661,6 +17983,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N233" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O233" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="17" customHeight="1">
       <c r="A234" s="7" t="inlineStr">
@@ -15712,6 +18044,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N234" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O234" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="17" customHeight="1">
       <c r="A235" s="7" t="inlineStr">
@@ -15763,6 +18105,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N235" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O235" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="17" customHeight="1">
       <c r="A236" s="7" t="inlineStr">
@@ -15814,6 +18166,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N236" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O236" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="17" customHeight="1">
       <c r="A237" s="7" t="inlineStr">
@@ -15865,6 +18227,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N237" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O237" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="17" customHeight="1">
       <c r="A238" s="7" t="inlineStr">
@@ -15916,6 +18288,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N238" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O238" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="17" customHeight="1">
       <c r="A239" s="7" t="inlineStr">
@@ -15967,6 +18349,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N239" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O239" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="17" customHeight="1">
       <c r="A240" s="7" t="inlineStr">
@@ -16018,6 +18410,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N240" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O240" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="17" customHeight="1">
       <c r="A241" s="7" t="inlineStr">
@@ -16069,6 +18471,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N241" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O241" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="17" customHeight="1">
       <c r="A242" s="7" t="inlineStr">
@@ -16120,6 +18532,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N242" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O242" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="17" customHeight="1">
       <c r="A243" s="7" t="inlineStr">
@@ -16171,6 +18593,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N243" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O243" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="17" customHeight="1">
       <c r="A244" s="7" t="inlineStr">
@@ -16222,6 +18654,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N244" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O244" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="17" customHeight="1">
       <c r="A245" s="7" t="inlineStr">
@@ -16273,6 +18715,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N245" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O245" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="17" customHeight="1">
       <c r="A246" s="7" t="inlineStr">
@@ -16324,6 +18776,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N246" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O246" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="17" customHeight="1">
       <c r="A247" s="7" t="inlineStr">
@@ -16375,6 +18837,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N247" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O247" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="17" customHeight="1">
       <c r="A248" s="7" t="inlineStr">
@@ -16426,6 +18898,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N248" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O248" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="17" customHeight="1">
       <c r="A249" s="7" t="inlineStr">
@@ -16477,6 +18959,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N249" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O249" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="17" customHeight="1">
       <c r="A250" s="7" t="inlineStr">
@@ -16528,6 +19020,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N250" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O250" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="17" customHeight="1">
       <c r="A251" s="7" t="inlineStr">
@@ -16579,6 +19081,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N251" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O251" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="17" customHeight="1">
       <c r="A252" s="7" t="inlineStr">
@@ -16630,6 +19142,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N252" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O252" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="17" customHeight="1">
       <c r="A253" s="7" t="inlineStr">
@@ -16681,6 +19203,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N253" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O253" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="17" customHeight="1">
       <c r="A254" s="7" t="inlineStr">
@@ -16732,6 +19264,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N254" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O254" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="17" customHeight="1">
       <c r="A255" s="7" t="inlineStr">
@@ -16783,6 +19325,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N255" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O255" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="17" customHeight="1">
       <c r="A256" s="7" t="inlineStr">
@@ -16834,6 +19386,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N256" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O256" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="17" customHeight="1">
       <c r="A257" s="7" t="inlineStr">
@@ -16885,6 +19447,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N257" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O257" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="17" customHeight="1">
       <c r="A258" s="7" t="inlineStr">
@@ -16936,6 +19508,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N258" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O258" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="17" customHeight="1">
       <c r="A259" s="7" t="inlineStr">
@@ -16987,6 +19569,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N259" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O259" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="17" customHeight="1">
       <c r="A260" s="7" t="inlineStr">
@@ -17038,6 +19630,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N260" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O260" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="17" customHeight="1">
       <c r="A261" s="7" t="inlineStr">
@@ -17089,6 +19691,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N261" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O261" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="17" customHeight="1">
       <c r="A262" s="7" t="inlineStr">
@@ -17140,6 +19752,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N262" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O262" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="17" customHeight="1">
       <c r="A263" s="7" t="inlineStr">
@@ -17191,6 +19813,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N263" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O263" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="17" customHeight="1">
       <c r="A264" s="7" t="inlineStr">
@@ -17242,6 +19874,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N264" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O264" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="17" customHeight="1">
       <c r="A265" s="7" t="inlineStr">
@@ -17293,6 +19935,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N265" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O265" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="17" customHeight="1">
       <c r="A266" s="7" t="inlineStr">
@@ -17344,6 +19996,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N266" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O266" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="17" customHeight="1">
       <c r="A267" s="7" t="inlineStr">
@@ -17395,6 +20057,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N267" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O267" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="17" customHeight="1">
       <c r="A268" s="7" t="inlineStr">
@@ -17446,6 +20118,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N268" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O268" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="17" customHeight="1">
       <c r="A269" s="7" t="inlineStr">
@@ -17497,6 +20179,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N269" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O269" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="17" customHeight="1">
       <c r="A270" s="7" t="inlineStr">
@@ -17548,6 +20240,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N270" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O270" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="17" customHeight="1">
       <c r="A271" s="7" t="inlineStr">
@@ -17599,6 +20301,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N271" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O271" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="17" customHeight="1">
       <c r="A272" s="7" t="inlineStr">
@@ -17650,6 +20362,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N272" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O272" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="17" customHeight="1">
       <c r="A273" s="7" t="inlineStr">
@@ -17701,6 +20423,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N273" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O273" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="17" customHeight="1">
       <c r="A274" s="7" t="inlineStr">
@@ -17752,6 +20484,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N274" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O274" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="17" customHeight="1">
       <c r="A275" s="7" t="inlineStr">
@@ -17803,6 +20545,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N275" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O275" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="17" customHeight="1">
       <c r="A276" s="7" t="inlineStr">
@@ -17854,6 +20606,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N276" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O276" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="17" customHeight="1">
       <c r="A277" s="7" t="inlineStr">
@@ -17905,6 +20667,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N277" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O277" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="17" customHeight="1">
       <c r="A278" s="7" t="inlineStr">
@@ -17956,6 +20728,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N278" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O278" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="17" customHeight="1">
       <c r="A279" s="7" t="inlineStr">
@@ -18007,6 +20789,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N279" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O279" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="17" customHeight="1">
       <c r="A280" s="7" t="inlineStr">
@@ -18058,6 +20850,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N280" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O280" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="17" customHeight="1">
       <c r="A281" s="7" t="inlineStr">
@@ -18109,6 +20911,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N281" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O281" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="17" customHeight="1">
       <c r="A282" s="7" t="inlineStr">
@@ -18160,6 +20972,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N282" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O282" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="17" customHeight="1">
       <c r="A283" s="7" t="inlineStr">
@@ -18211,6 +21033,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N283" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O283" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="17" customHeight="1">
       <c r="A284" s="7" t="inlineStr">
@@ -18262,6 +21094,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N284" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O284" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="17" customHeight="1">
       <c r="A285" s="7" t="inlineStr">
@@ -18313,6 +21155,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N285" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O285" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="17" customHeight="1">
       <c r="A286" s="7" t="inlineStr">
@@ -18364,6 +21216,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N286" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O286" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="17" customHeight="1">
       <c r="A287" s="7" t="inlineStr">
@@ -18415,6 +21277,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N287" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O287" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="17" customHeight="1">
       <c r="A288" s="7" t="inlineStr">
@@ -18466,6 +21338,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N288" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O288" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="17" customHeight="1">
       <c r="A289" s="7" t="inlineStr">
@@ -18517,6 +21399,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N289" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O289" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="17" customHeight="1">
       <c r="A290" s="7" t="inlineStr">
@@ -18568,6 +21460,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N290" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O290" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="17" customHeight="1">
       <c r="A291" s="7" t="inlineStr">
@@ -18619,6 +21521,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N291" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O291" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="17" customHeight="1">
       <c r="A292" s="7" t="inlineStr">
@@ -18670,6 +21582,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N292" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O292" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="17" customHeight="1">
       <c r="A293" s="7" t="inlineStr">
@@ -18721,6 +21643,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N293" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O293" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="17" customHeight="1">
       <c r="A294" s="7" t="inlineStr">
@@ -18772,6 +21704,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N294" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O294" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="17" customHeight="1">
       <c r="A295" s="7" t="inlineStr">
@@ -18823,6 +21765,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N295" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O295" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="17" customHeight="1">
       <c r="A296" s="7" t="inlineStr">
@@ -18874,6 +21826,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N296" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O296" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="17" customHeight="1">
       <c r="A297" s="7" t="inlineStr">
@@ -18925,6 +21887,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N297" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O297" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="17" customHeight="1">
       <c r="A298" s="7" t="inlineStr">
@@ -18976,6 +21948,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N298" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O298" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="17" customHeight="1">
       <c r="A299" s="7" t="inlineStr">
@@ -19027,6 +22009,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N299" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O299" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="17" customHeight="1">
       <c r="A300" s="7" t="inlineStr">
@@ -19078,6 +22070,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N300" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O300" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="17" customHeight="1">
       <c r="A301" s="7" t="inlineStr">
@@ -19129,6 +22131,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N301" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O301" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="17" customHeight="1">
       <c r="A302" s="7" t="inlineStr">
@@ -19180,6 +22192,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N302" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O302" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="17" customHeight="1">
       <c r="A303" s="7" t="inlineStr">
@@ -19231,6 +22253,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N303" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O303" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="17" customHeight="1">
       <c r="A304" s="7" t="inlineStr">
@@ -19282,6 +22314,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N304" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O304" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="17" customHeight="1">
       <c r="A305" s="7" t="inlineStr">
@@ -19333,6 +22375,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N305" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O305" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="17" customHeight="1">
       <c r="A306" s="7" t="inlineStr">
@@ -19384,6 +22436,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N306" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O306" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="17" customHeight="1">
       <c r="A307" s="7" t="inlineStr">
@@ -19435,6 +22497,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N307" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O307" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="17" customHeight="1">
       <c r="A308" s="7" t="inlineStr">
@@ -19486,6 +22558,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N308" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O308" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="17" customHeight="1">
       <c r="A309" s="7" t="inlineStr">
@@ -19537,6 +22619,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N309" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O309" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="17" customHeight="1">
       <c r="A310" s="7" t="inlineStr">
@@ -19588,6 +22680,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N310" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O310" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="17" customHeight="1">
       <c r="A311" s="7" t="inlineStr">
@@ -19639,6 +22741,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N311" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O311" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="17" customHeight="1">
       <c r="A312" s="7" t="inlineStr">
@@ -19690,6 +22802,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N312" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O312" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="17" customHeight="1">
       <c r="A313" s="7" t="inlineStr">
@@ -19741,9 +22863,19 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N313" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O313" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M313"/>
+  <autoFilter ref="A1:O313"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19754,10 +22886,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -19793,7 +22925,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>ad1b0e0037e348d336137ef88ca756f886fb2a05f5ee3b30ee1c6c4b6de3a67e</t>
+          <t>6505e759a454745728d7d6f8f6d3a34234f64af785bfe0e0f1ef36497a357de3</t>
         </is>
       </c>
     </row>
@@ -19832,65 +22964,117 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>cells</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>288</v>
+          <t>Export type</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Draft Excel</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>cells with source boxes</t>
+          <t>Non-empty exported cells</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>equations</t>
+          <t>Cells with source boxes</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>equation checks</t>
+          <t>Cells requiring full-page evidence review</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>failed equation checks</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>0</v>
+          <t>Cell source-box coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>cells with source boxes</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>equations</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>equation checks</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>failed equation checks</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>proposals with multiple equations</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B17" s="7" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
